--- a/data/trans_orig/IP16A11_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16A11_2023-Edad-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9298</t>
+          <t>8957</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8930</t>
+          <t>8594</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7348</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>16114</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>41,59%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7093</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13091</t>
+          <t>13249</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13427</t>
+          <t>13763</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19517</t>
+          <t>19491</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23247</t>
+          <t>22634</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31400</t>
+          <t>31536</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,39%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10660</t>
+          <t>10294</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21594</t>
+          <t>20789</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9981</t>
+          <t>10405</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21296</t>
+          <t>21042</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23480</t>
+          <t>23203</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38947</t>
+          <t>38675</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,45%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25029</t>
+          <t>25834</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35963</t>
+          <t>36329</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27688</t>
+          <t>27942</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39003</t>
+          <t>38579</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56660</t>
+          <t>56932</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72127</t>
+          <t>72404</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,73%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>13988</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23624</t>
+          <t>23777</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>9881</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21913</t>
+          <t>22130</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26740</t>
+          <t>27661</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42487</t>
+          <t>43047</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,66%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13527</t>
+          <t>13374</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23850</t>
+          <t>23163</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24256</t>
+          <t>24039</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35626</t>
+          <t>36288</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40833</t>
+          <t>40273</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56580</t>
+          <t>55659</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>66,8%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>5049</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28976</t>
+          <t>28882</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15356</t>
+          <t>14593</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30881</t>
+          <t>30278</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22015</t>
+          <t>22308</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54203</t>
+          <t>54020</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,41%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50210</t>
+          <t>50304</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72913</t>
+          <t>74137</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34319</t>
+          <t>34922</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49844</t>
+          <t>50607</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>90182</t>
+          <t>90365</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>122370</t>
+          <t>122077</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,55%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>35717</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>72844</t>
+          <t>73114</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>48224</t>
+          <t>47794</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71335</t>
+          <t>69961</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86219</t>
+          <t>90094</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>133730</t>
+          <t>134078</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,03%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>106508</t>
+          <t>106238</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>145559</t>
+          <t>143635</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>111374</t>
+          <t>112748</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>134485</t>
+          <t>134915</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>228331</t>
+          <t>227983</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>275842</t>
+          <t>271967</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A11_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16A11_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8957</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8594</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11171</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16114</t>
+          <t>13204</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,38%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13351</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10371</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>15239</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>76,59%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>59,49%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>87,41%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>10478</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7434</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13249</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>63,93%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>45,35%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>80,83%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17099</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13763</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19491</t>
+          <t>11395</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>27577</t>
+          <t>22483</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22634</t>
+          <t>18706</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31536</t>
+          <t>25470</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>79,82%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>16391</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>16391</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>16391</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14477</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14477</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14477</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>38748</t>
+          <t>31910</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38748</t>
+          <t>31910</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38748</t>
+          <t>31910</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15578</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10294</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20789</t>
+          <t>17513</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15190</t>
+          <t>14278</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10405</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21042</t>
+          <t>19375</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>30767</t>
+          <t>26966</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23203</t>
+          <t>20939</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38675</t>
+          <t>33644</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,96%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28547</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23722</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>32933</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>69,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>57,53%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>79,87%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>31045</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>25834</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>36329</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>66,59%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>55,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>77,92%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>33794</t>
+          <t>26618</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27942</t>
+          <t>21521</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38579</t>
+          <t>31105</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>64840</t>
+          <t>55165</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56932</t>
+          <t>48487</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72404</t>
+          <t>61192</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>74,51%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14882</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9873</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20595</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>33,84%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>22,45%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>46,84%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>18890</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13988</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23777</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>50,85%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,65%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>64,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15638</t>
+          <t>19514</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9881</t>
+          <t>13675</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22130</t>
+          <t>24195</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>34528</t>
+          <t>34396</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27661</t>
+          <t>25781</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43047</t>
+          <t>42169</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,48%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>29089</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>23376</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>34098</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>66,16%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>53,16%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>77,55%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>18261</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>13374</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>23163</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>49,15%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>36,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>62,35%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30531</t>
+          <t>18434</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24039</t>
+          <t>13753</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36288</t>
+          <t>24273</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>48792</t>
+          <t>47523</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40273</t>
+          <t>39750</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>55659</t>
+          <t>56138</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>68,53%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>21200</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14012</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>29280</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>33,74%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>22,3%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>46,59%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>16625</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5049</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>28882</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>20,99%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,38%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>36,47%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22483</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14593</t>
+          <t>11889</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30278</t>
+          <t>23284</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>39107</t>
+          <t>38268</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22308</t>
+          <t>28798</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54020</t>
+          <t>48488</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>42,47%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>41640</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>33560</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>48828</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>66,26%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>53,41%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>77,7%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>62561</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>50304</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>74137</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>79,01%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>63,53%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,62%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>42717</t>
+          <t>34252</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34922</t>
+          <t>28036</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50607</t>
+          <t>39431</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>105278</t>
+          <t>75892</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>90365</t>
+          <t>65672</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>122077</t>
+          <t>85362</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>74,77%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>62840</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>62840</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>62840</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>79186</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>79186</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>79186</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>65200</t>
+          <t>51320</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>65200</t>
+          <t>51320</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>65200</t>
+          <t>51320</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>144385</t>
+          <t>114160</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>144385</t>
+          <t>114160</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>144385</t>
+          <t>114160</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>52852</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>42683</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>63754</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>31,94%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>25,79%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>38,53%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>57005</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>35717</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>73114</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>31,78%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>19,91%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>40,77%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>58569</t>
+          <t>56204</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47794</t>
+          <t>47419</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69961</t>
+          <t>66158</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>115574</t>
+          <t>109056</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90094</t>
+          <t>93456</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134078</t>
+          <t>121778</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>39,27%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>112627</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>101725</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>122796</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>68,06%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>61,47%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>74,21%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>122347</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>106238</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>143635</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>68,22%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>59,23%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>80,09%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>124140</t>
+          <t>88437</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>112748</t>
+          <t>78483</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>134915</t>
+          <t>97222</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>246487</t>
+          <t>201064</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>227983</t>
+          <t>188342</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>271967</t>
+          <t>216664</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>69,86%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>165479</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>165479</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>165479</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>179352</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>179352</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>179352</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>144641</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>144641</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>144641</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>362061</t>
+          <t>310120</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>362061</t>
+          <t>310120</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>362061</t>
+          <t>310120</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
